--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Martabe tanpa SWI" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SWI vs Martabe'!$A$1:$E$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SWI vs Martabe'!$A$1:$H$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -94,6 +94,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -467,6 +470,9 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="95" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +501,21 @@
           <t>Perbedaan SWI dengan data Martabe</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Format Heritage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tanggal konversi</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Catatan konversi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -520,6 +541,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Dikonversi dari 304-008 heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-001.md</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -545,6 +581,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -570,6 +613,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -595,6 +645,13 @@
           <t>Martabe mengukur karbon yang terbawa ke launder (indikasi kehilangan karbon); SWI hanya mengukur larutan. Sumber Martabe tidak menyebut tujuan, volume sampler, suhu dan lama oven, sehingga rumus konsentrasi tidak ada. Bahaya Martabe: percikan slurry, sampler membentur kepala, titik jepit tutup titik sampling.</t>
         </is>
       </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -622,6 +679,13 @@
 2. Seluruhnya tambahan. Martabe memakai batas alarm HCN di bawah 10 ppm, SWI 5 ppm (SWI diterapkan). Angka plus-minus rentang di sumber tidak jelas.</t>
         </is>
       </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -647,6 +711,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -672,6 +743,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -697,6 +775,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -722,6 +807,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -747,6 +839,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -772,6 +871,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -797,6 +903,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -826,6 +939,13 @@
 3. Seluruhnya tambahan. Sumber tidak memberi pH akhir pembilasan atau kekuatan asam, dan tidak menyebut risiko HCN dari asam pada sianida.</t>
         </is>
       </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -851,6 +971,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -876,6 +1003,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -901,6 +1035,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -926,6 +1067,13 @@
           <t>Tambahan; mendukung 204-010 (kekuatan larutan). Hazard Martabe: kontak flokulan, lantai licin, titik jepit valve, jangan sampling saat ada pengangkatan flokulan.</t>
         </is>
       </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -951,6 +1099,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -976,6 +1131,13 @@
           <t>Martabe untuk filter air potabel, bukan discharge WTP berlisensi, sehingga hanya dijadikan referensi teknik; SWI tetap NOT FOR USE. 'SLS' dan paket assay tidak didefinisikan.</t>
         </is>
       </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1005,6 +1167,13 @@
 3. Titik sampel berbeda (pipa drain pompa); perlu konfirmasi pipa itu membawa larutan encer. Titran H2SO4 (rasio 2:1) vs HCl (1:1).</t>
         </is>
       </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1030,6 +1199,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1057,6 +1233,13 @@
 2. Tambahan. Toleransi hanya lewat contoh (sekitar 0.2 pH) padahal batas keselamatan sianida pH di atas 10.5; buffer hanya 7 dan 10 (SWI 206-004 memakai 4, 7, 10).</t>
         </is>
       </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1082,6 +1265,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1107,6 +1297,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1132,6 +1329,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1157,6 +1361,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1182,6 +1393,13 @@
           <t>Martabe memakai komposit banyak cuplikan dan pembanding persen padatan di lab; SWI memakai cut berwaktu dan tonase. Prinsip sama (jangan disetel sendiri). Martabe meminta control room mematikan pompa barren dan sump (alasan tidak disebut; daftar milik Martabe); rumus persen padatan tidak ada.</t>
         </is>
       </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1207,6 +1425,13 @@
           <t>Martabe hanya teknik pengambilan sampel (tanpa analisis ukuran); SWI hanya prinsip. Ditulis untuk ball mill dan VertiMill; pabrik Anda memakai IsaMill. Titik jangkar harness dan fungsi saklar tidak dijelaskan.</t>
         </is>
       </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1232,6 +1457,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1257,6 +1489,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1282,6 +1521,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1307,6 +1553,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1332,6 +1585,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1357,6 +1617,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -1382,6 +1649,13 @@
           <t>Martabe berbasis pengukuran celah dan umur screen, SWI berbasis kehilangan massa. Sumber menyebut bahaya tetapi tidak memberi kontrol. Perlu konfirmasi ada intertank screen dalam tangki dan batas 1.4 mm terhadap register aperture.</t>
         </is>
       </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1407,6 +1681,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1432,6 +1713,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1457,6 +1745,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1482,6 +1777,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1507,6 +1809,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -1532,6 +1841,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -1557,6 +1873,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -1582,6 +1905,13 @@
           <t>Martabe memverifikasi alat, bukan metode sampel. Tidak ada nilai penerimaan (teoretis sekitar 15.7 persen air). Moisture analyser tidak ada di daftar alat SWI. WI CV004 juga memakai oven 105 derajat C minimal 24 jam untuk bagian lab (tidak dimasukkan).</t>
         </is>
       </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -1607,6 +1937,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -1634,6 +1971,13 @@
 2. Tambahan. Sumber menyebut standar ASTM tetapi tanpa volume isi, ayakan partikel kasar atau hasil detik per quart; hanya cek cepat, bukan kurva rheologi.</t>
         </is>
       </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -1659,6 +2003,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -1688,6 +2039,13 @@
 3. Tambahan; rumus dosis terkonfirmasi (dosis x massa slurry x persen padatan / (kekuatan x 1.000.000)). Sumber tidak mencantumkan kontrol HCN padahal tailing bersianida; titik sampel dan pompa PU-372 milik Martabe.</t>
         </is>
       </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -1713,6 +2071,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -1738,6 +2103,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -1763,6 +2135,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -1788,6 +2167,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -1813,6 +2199,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -1838,6 +2231,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -1863,6 +2263,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -1888,6 +2295,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -1913,6 +2327,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -1938,6 +2359,13 @@
           <t>SWI lebih lengkap dan dipertahankan. Dari Martabe hanya dua hal: cek buret digital terbaca 0.00 dan cek kedaluwarsa AgNO3. Titik akhir Martabe 'merah muda' tidak dipakai.</t>
         </is>
       </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -1965,6 +2393,13 @@
 2. Bertentangan: titik akhir 'soft pink' keliru (fenolftalein tidak berwarna pada titik akhir); SWI dipakai. Titran '5 persen' bukan molaritas, harus distandarisasi.</t>
         </is>
       </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -1990,6 +2425,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -2015,6 +2457,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2040,6 +2489,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -2069,6 +2525,13 @@
 3. Tambahan. V1.2 tidak punya langkah ulang dengan kaustik padahal tabelnya ada; satuan konsumsi mL/L untuk reagen padat; data berisi salah ketik. Satu penambahan 0.5 g melompatkan pH dari 6.2 ke 9.58 sehingga dosis perlu lebih kecil mendekati pH 7.</t>
         </is>
       </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -2094,6 +2557,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -2119,6 +2589,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -2144,6 +2621,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -2169,6 +2653,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -2194,6 +2685,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -2225,6 +2723,13 @@
 4. Versi lebih awal dari uji adsorpsi slurry; tujuan H2SO4 5 persen dan 1 persen tidak dijelaskan.</t>
         </is>
       </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -2262,6 +2767,13 @@
 7. Tambahan. Kalibrasi memakai air; perlu konfirmasi pada laju uji (150 dan 300 mL/jam).</t>
         </is>
       </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -2287,6 +2799,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -2312,6 +2831,13 @@
           <t>Martabe hanya langkah lime; tujuan menyebut peroxide tanpa dosis; pH awal dan kandungan sianida tidak disebut; PPE di bawah standar. Rute detox tidak tercakup.</t>
         </is>
       </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -2337,6 +2863,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -2362,6 +2895,13 @@
           <t>Bertentangan dengan Part A. Saya batasi ke indikator dan desikan saja, bukan standar atau sianida, dan perlu persetujuan kebijakan. Suhu oven tidak disebut.</t>
         </is>
       </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -2387,6 +2927,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -2412,6 +2959,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -2437,6 +2991,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -2462,6 +3023,13 @@
           <t>Tambahan ukur kuantitatif. Tidak ada nilai penerimaan dan cara merata-ratakan.</t>
         </is>
       </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -2487,6 +3055,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -2516,6 +3091,13 @@
 3. Bertentangan: tiga titik (SWI) vs dua titik; SWI dipertahankan kecuali dua titik disetujui. Martabe tidak mencatat slope dan offset.</t>
         </is>
       </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -2541,6 +3123,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -2566,6 +3155,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -2591,6 +3187,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -2616,6 +3219,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -2641,6 +3251,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -2666,6 +3283,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -2691,6 +3315,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -2716,6 +3347,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -2741,6 +3379,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -2766,6 +3411,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -2791,6 +3443,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -2816,6 +3475,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -2841,6 +3507,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -2866,6 +3539,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -2891,6 +3571,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
@@ -2916,6 +3603,13 @@
           <t>Sumber meminta alarm HCN di bawah 10 ppm; SWI 5 ppm (diterapkan). Langkah mengacu foto yang tidak ikut; perangkat HCl Martabe belum tentu ada di Cynoprobe Anda. Operasi harian tidak tercakup.</t>
         </is>
       </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
@@ -2943,6 +3637,13 @@
 2. Standar detox tidak konsisten di sumber; perlu dipetakan ke analyser 051-CA-002.</t>
         </is>
       </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -2968,6 +3669,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -2993,6 +3701,13 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -3018,9 +3733,21 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Belum</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E100"/>
+  <autoFilter ref="A1:H100"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Sudah,Belum"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -583,11 +583,19 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dikonversi ke format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-002-003.md</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -615,11 +623,19 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Dikonversi ke format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-002-003.md</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -663,11 +663,19 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; carbon-in-launder (Martabe WI-00058) jadi Step 5, DRAFT; lihat docs/Format-Heritage/Catatan-Perubahan-201-004.md</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -705,11 +705,19 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; C2 check (Step 4) dan C2 calibration (Step 5) dari Martabe, DRAFT; lihat docs/Format-Heritage/Catatan-Perubahan-201-005.md</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Format Heritage; C2 check (Step 4) dan C2 calibration (Step 5) dari Martabe, DRAFT; lihat docs/Format-Heritage/Catatan-Perubahan-201-005.md</t>
+          <t>Format Heritage; bagian Martabe (C2 check, C2 calibration) dibuang karena plant tidak punya analyser C2; lihat docs/Format-Heritage/Catatan-Perubahan-201-005.md</t>
         </is>
       </c>
     </row>

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -745,11 +745,19 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-006-012.md</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -777,11 +785,19 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-006-012.md</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -809,11 +825,19 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-006-012.md</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -841,11 +865,19 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-006-012.md</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -873,11 +905,19 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-006-012.md</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -905,11 +945,19 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-006-012.md</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -937,11 +985,19 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-006-012.md</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1029,11 +1029,19 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; Part B, C, D Martabe disetujui dan dimasukkan (Step 3-5, DRAFT); lihat docs/Format-Heritage/Catatan-Perubahan-201-013.md</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1069,11 +1069,19 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-014-016.md</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1101,11 +1109,19 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-014-016.md</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1133,11 +1149,19 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-014-016.md</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1189,11 +1189,19 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; flocculant solution sampling (Martabe WI-00064) dipindah ke 201-020 (area reagent); lihat docs/Format-Heritage/Catatan-Perubahan-201-017-020.md</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1289,11 +1297,19 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; Part B, C, D Martabe dan flocculant solution sampling (dari 201-017) sebagai Step 4-7, DRAFT; lihat docs/Format-Heritage/Catatan-Perubahan-201-017-020.md</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1229,11 +1229,19 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-018.md</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1269,11 +1269,19 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; teknik sampling Martabe jadi Step 2-3; NOT FOR USE diganti catatan: titik sampling perlu diupdate; lihat docs/Format-Heritage/Catatan-Perubahan-201-019.md</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1353,11 +1353,19 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-021-025.md</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1387,11 +1395,19 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-021-025.md; Part B dan C Martabe jadi Step 4-5, DRAFT</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1419,11 +1435,19 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-021-025.md</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1451,11 +1475,19 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-021-025.md</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1483,11 +1515,19 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-201-021-025.md</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1555,11 +1555,19 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1651,11 +1659,19 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1683,11 +1699,19 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1715,11 +1739,19 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1747,11 +1779,19 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1779,11 +1819,19 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1811,11 +1859,19 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -1875,11 +1931,19 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1907,11 +1971,19 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-203-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1595,11 +1595,19 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; metode Martabe (sampling manual) tidak dimasukkan karena SWI memakai cutter dengan pompa; lihat docs/Format-Heritage/Catatan-Perubahan-203-002-003.md</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1627,11 +1635,19 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; metode Martabe (sampling manual) tidak dimasukkan karena SWI memakai cutter dengan pompa; lihat docs/Format-Heritage/Catatan-Perubahan-203-002-003.md</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -1915,11 +1915,19 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; Part B Martabe (angkat intertank screen saat shutdown) tidak dimasukkan: inspeksi perawatan, bukan pengecekan rutin; lihat docs/Format-Heritage/Catatan-Perubahan-203-010.md</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -2035,11 +2035,19 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2067,11 +2075,19 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2099,11 +2115,19 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md; tetap NOT FOR USE (laser sizer belum dibeli)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2131,11 +2155,19 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2163,11 +2195,19 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -2227,11 +2267,19 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -2293,11 +2341,19 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -2361,11 +2417,19 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2393,11 +2457,19 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2425,11 +2497,19 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2457,11 +2537,19 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2489,11 +2577,19 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2521,11 +2617,19 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2553,11 +2657,19 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2585,11 +2697,19 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -2617,11 +2737,19 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-204-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -2235,11 +2235,19 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; Part B Martabe (moisture analyser A&amp;D MS-70) dibuang - Mt. Morgan tidak punya moisture analyser; lihat docs/Format-Heritage/Catatan-Perubahan-204-006-008-010.md</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2309,11 +2317,19 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; cara Martabe dipakai dengan alat yang sama (Brookfield DV2TLV dan Marsh funnel), DRAFT sampai JSEA diperbarui; lihat docs/Format-Heritage/Catatan-Perubahan-204-006-008-010.md</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2385,11 +2401,19 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; Part B, C, D Martabe disetujui sebagai Step 4-8, DRAFT; gelas ukur 1 L disetujui untuk Part A; lihat docs/Format-Heritage/Catatan-Perubahan-204-006-008-010.md</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -3853,11 +3853,19 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; tetap NOT FOR USE (desain sampler dan cutter belum ada); lihat docs/Format-Heritage/Catatan-Perubahan-207-001-006.md</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -3885,11 +3893,19 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="n"/>
-      <c r="H91" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; tetap NOT FOR USE (desain sampler dan cutter belum ada); lihat docs/Format-Heritage/Catatan-Perubahan-207-001-006.md</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -3917,11 +3933,19 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; tetap NOT FOR USE (desain sampler dan cutter belum ada); lihat docs/Format-Heritage/Catatan-Perubahan-207-001-006.md</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -3949,11 +3973,19 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; tetap NOT FOR USE (desain sampler dan cutter belum ada); lihat docs/Format-Heritage/Catatan-Perubahan-207-001-006.md</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -3981,11 +4013,19 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="n"/>
-      <c r="H94" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; tetap NOT FOR USE (desain sampler dan cutter belum ada); lihat docs/Format-Heritage/Catatan-Perubahan-207-001-006.md</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -4013,11 +4053,19 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; lihat docs/Format-Heritage/Catatan-Perubahan-207-001-006.md</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -4093,11 +4093,19 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="n"/>
-      <c r="H96" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; operasi harian tetap NOT FOR USE (manual Cynoprobe belum ada); ganti filter sock Martabe jadi Step 3, DRAFT; lihat docs/Format-Heritage/Catatan-Perubahan-207-007-011.md</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
@@ -4127,11 +4135,19 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="n"/>
-      <c r="H97" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; kalibrasi leach analyser Martabe dipakai untuk kedua analyser, DRAFT; kalibrasi detox dibuang (tidak ada sirkuit detox, ReCYN setelah CIL); lihat docs/Format-Heritage/Catatan-Perubahan-207-007-011.md</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -4159,11 +4175,19 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="n"/>
-      <c r="H98" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; tetap NOT FOR USE (manual Cynoprobe belum ada); lihat docs/Format-Heritage/Catatan-Perubahan-207-007-011.md</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -4191,11 +4215,19 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="n"/>
-      <c r="H99" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; tetap NOT FOR USE (manual pompa Vender Dura 10 belum ada); lihat docs/Format-Heritage/Catatan-Perubahan-207-007-011.md</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -4223,11 +4255,19 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="n"/>
-      <c r="H100" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; tetap NOT FOR USE (dokumen vendor leak detector dan level switch belum ada); respons sementara dipertahankan; lihat docs/Format-Heritage/Catatan-Perubahan-207-007-011.md</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H100"/>

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -4145,7 +4145,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Format Heritage; kalibrasi leach analyser Martabe dipakai untuk kedua analyser, DRAFT; kalibrasi detox dibuang (tidak ada sirkuit detox, ReCYN setelah CIL); lihat docs/Format-Heritage/Catatan-Perubahan-207-007-011.md</t>
+          <t>Format Heritage; kalibrasi leach analyser Martabe untuk 032-CA-001 (Step 2-5); kalibrasi detox Martabe dipetakan ke analyser ReCYN tailing 051-CA-002 (Step 6), DRAFT; lihat docs/Format-Heritage/Catatan-Perubahan-207-007-011.md</t>
         </is>
       </c>
     </row>

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -3433,11 +3433,19 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -3497,11 +3505,19 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -3565,11 +3581,19 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -3597,11 +3621,19 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -3629,11 +3661,19 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -3661,11 +3701,19 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -3693,11 +3741,19 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="n"/>
-      <c r="H85" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; APD ditambah proteksi telinga (bench mill), sesuai persetujuan 204; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -3725,11 +3781,19 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="n"/>
-      <c r="H86" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -3757,11 +3821,19 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="n"/>
-      <c r="H87" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -3789,11 +3861,19 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="n"/>
-      <c r="H88" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -3821,11 +3901,19 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO210; lihat docs/Format-Heritage/Catatan-Perubahan-206-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -3473,11 +3473,19 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="n"/>
-      <c r="H78" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; DRAFT - anemometer GM8902 Martabe jadi Step 4-5: ukur di tinggi sash kerja, catat rata-rata dan bacaan terendah dari 20 bacaan, nilai penerimaan dari spesifikasi Safetyflow atau AS/NZS 2243.8 (open item), frekuensi bulanan; lihat docs/Format-Heritage/Catatan-Perubahan-206-002-004.md</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -3549,11 +3557,19 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; DRAFT - TPS cube dipakai seperti Martabe (Step 3-4), kalibrasi pH tetap 3 titik dengan slope dan offset; metode DO Martabe untuk HI9142 tanpa menu Oxyguard, nilai 6-8 tidak dipakai (Step 5-6); latex diganti sarung tangan tahan bahan kimia; lihat docs/Format-Heritage/Catatan-Perubahan-206-002-004.md</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -2867,11 +2867,19 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -2899,11 +2907,19 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2931,11 +2947,19 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -2999,11 +3023,19 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -3031,11 +3063,19 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3063,11 +3103,19 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; safety-critical, kerja sianida tidak sendirian; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -3095,11 +3143,19 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -3127,11 +3183,19 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; APD ditambah pelindung telinga (hazard hearing damage, Ro-Tap); lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -3241,11 +3305,19 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; APD ditambah pelindung telinga (hazard hearing damage, Ro-Tap); lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -3305,11 +3377,19 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -3369,11 +3449,19 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -3401,11 +3489,19 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; isi SWI dipertahankan, tidak ada padanan Martabe; Parent procedure HM-PRC-VXX-PRO209; lihat docs/Format-Heritage/Catatan-Perubahan-205-batch1.md</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">

--- a/docs/Tabel-SWI-vs-Martabe.xlsx
+++ b/docs/Tabel-SWI-vs-Martabe.xlsx
@@ -2801,11 +2801,19 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; Final - isi SWI tetap, dari Martabe hanya cek buret digital 0.00 dan kedaluwarsa AgNO3; titik akhir salmon pink 30 detik; lihat docs/Format-Heritage/Catatan-Perubahan-205-Martabe.md</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -2835,11 +2843,19 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; DRAFT - HCl tetap utama, H2SO4 alternatif (faktor 2, x40 untuk g/L, titrant distandarisasi), titik akhir pink hilang 30 detik; lihat docs/Format-Heritage/Catatan-Perubahan-205-Martabe.md</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -2991,11 +3007,19 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; DRAFT - Part B-D Martabe dan TSF Toe digabung jadi satu metode netralisasi air asam, hanya sampel bebas sianida; nama sampel dan angka tabel Martabe tidak dipakai; lihat docs/Format-Heritage/Catatan-Perubahan-205-Martabe.md</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3229,11 +3253,19 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; DRAFT NOT FOR USE - pH &gt;=10.5, sampel 20 mL, varian KCN dibuang, CIL 7 -&gt; 032-TK-006 ke ReCYN, slurry 5 L; kapasitas loading dan data Goldquip open item; lihat docs/Format-Heritage/Catatan-Perubahan-205-Martabe.md</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -3273,11 +3305,19 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; DRAFT NOT FOR USE, safety-critical - V2 sebagai dasar, pH &gt;=10.5 sebelum sianida, AgNO3 0.1/0.01 M, sulfamic acid dijaga 240 menit, KCN heptahydrate; urutan pencampuran Zn(CN)4 jadi open item; lihat docs/Format-Heritage/Catatan-Perubahan-205-Martabe.md</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -3345,11 +3385,19 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; NOT FOR USE - tidak ada sirkuit detox (ReCYN setelah CIL), keputusan OR-07 terbuka; TSF Toe dipindah ke 205-006; lihat docs/Format-Heritage/Catatan-Perubahan-205-Martabe.md</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -3417,11 +3465,19 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Belum</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="2" t="n"/>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Format Heritage; DRAFT - re-kualifikasi hanya phenolphthalein dan silica gel, perlu persetujuan Metallurgy Superintendent; suhu oven dari SDS; lihat docs/Format-Heritage/Catatan-Perubahan-205-Martabe.md</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
